--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
   <si>
     <t>Неделя</t>
   </si>
@@ -169,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -222,11 +222,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -238,44 +251,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -289,15 +272,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -308,20 +282,62 @@
     <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -642,7 +658,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" thickBot="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="40" t="s">
@@ -665,82 +681,82 @@
         <v>7</v>
       </c>
       <c r="K1" s="40"/>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16" t="s">
+      <c r="M1" s="39"/>
+      <c r="N1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16" t="s">
+      <c r="O1" s="39"/>
+      <c r="P1" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16" t="s">
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="U1" s="8" t="s">
+      <c r="S1" s="39"/>
+      <c r="U1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="30"/>
+      <c r="V1" s="17"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="17">
+      <c r="A2" s="34">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="37" t="s">
+      <c r="G2" s="28"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37" t="s">
+      <c r="M2" s="28"/>
+      <c r="N2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="37"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="19"/>
-      <c r="U2" s="31" t="s">
+      <c r="O2" s="28"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="U2" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="32"/>
+      <c r="V2" s="19"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="12"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="2"/>
@@ -754,207 +770,211 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="8"/>
-      <c r="U3" s="36" t="s">
+      <c r="S3" s="7"/>
+      <c r="U3" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="V3" s="30"/>
+      <c r="V3" s="17"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="12"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="14" t="s">
+      <c r="A4" s="35"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="14"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="U4" s="13" t="s">
+      <c r="O4" s="38"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="U4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="V4" s="32"/>
+      <c r="V4" s="19"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="20"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="24"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="14"/>
       <c r="U5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="32"/>
+      <c r="V5" s="19"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="17">
+      <c r="A6" s="34">
         <v>2</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37" t="s">
+      <c r="E6" s="28"/>
+      <c r="F6" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37" t="s">
+      <c r="G6" s="28"/>
+      <c r="H6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37" t="s">
+      <c r="I6" s="28"/>
+      <c r="J6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="37"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="38" t="s">
+      <c r="K6" s="28"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="38"/>
-      <c r="P6" s="37" t="s">
+      <c r="O6" s="37"/>
+      <c r="P6" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37" t="s">
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="37"/>
-      <c r="U6" s="9" t="s">
+      <c r="S6" s="28"/>
+      <c r="U6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="V6" s="32"/>
+      <c r="V6" s="19"/>
     </row>
     <row r="7" spans="1:22" ht="15" thickBot="1">
-      <c r="A7" s="20"/>
-      <c r="B7" s="22" t="s">
+      <c r="A7" s="36"/>
+      <c r="B7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="15"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q7" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="U7" s="34" t="s">
+      <c r="H7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="U7" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="V7" s="32"/>
+      <c r="V7" s="19"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37" t="s">
+      <c r="C8" s="28"/>
+      <c r="D8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37" t="s">
+      <c r="E8" s="28"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37" t="s">
+      <c r="G8" s="28"/>
+      <c r="H8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="37"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="35" t="s">
+      <c r="I8" s="28"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35" t="s">
+      <c r="M8" s="33"/>
+      <c r="N8" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="35"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="32"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="19"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="28"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="4"/>
+      <c r="H9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -964,81 +984,80 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="8"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="32"/>
+      <c r="S9" s="7"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="19"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="28"/>
-      <c r="B10" s="39" t="s">
+      <c r="A10" s="30"/>
+      <c r="B10" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="7" t="s">
+      <c r="C10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="32"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="19"/>
     </row>
     <row r="11" spans="1:22" ht="15" thickBot="1">
-      <c r="A11" s="29"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="24"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -1055,26 +1074,27 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>Неделя</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>ТЕКУЩАЯ НЕДЕЛЯ</t>
+  </si>
+  <si>
+    <t>ДЗ 3</t>
   </si>
 </sst>
 </file>
@@ -283,61 +286,61 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -645,8 +648,8 @@
     <col min="7" max="7" width="8.88671875" style="6"/>
     <col min="8" max="8" width="8.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.21875" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.21875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
     <col min="12" max="12" width="8.88671875" style="1"/>
     <col min="13" max="13" width="8.88671875" style="6"/>
     <col min="14" max="14" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -661,86 +664,86 @@
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40" t="s">
+      <c r="C1" s="26"/>
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40" t="s">
+      <c r="G1" s="26"/>
+      <c r="H1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40" t="s">
+      <c r="I1" s="26"/>
+      <c r="J1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="40"/>
-      <c r="L1" s="39" t="s">
+      <c r="K1" s="26"/>
+      <c r="L1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39" t="s">
+      <c r="M1" s="23"/>
+      <c r="N1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39" t="s">
+      <c r="O1" s="23"/>
+      <c r="P1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39" t="s">
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="39"/>
+      <c r="S1" s="23"/>
       <c r="U1" s="7" t="s">
         <v>25</v>
       </c>
       <c r="V1" s="17"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="34">
+      <c r="A2" s="29">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28" t="s">
+      <c r="E2" s="24"/>
+      <c r="F2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="28" t="s">
+      <c r="G2" s="24"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28" t="s">
+      <c r="M2" s="24"/>
+      <c r="N2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="28"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="U2" s="18" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="19"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="35"/>
+      <c r="A3" s="30"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -777,34 +780,34 @@
       <c r="V3" s="17"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="35"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="38" t="s">
+      <c r="A4" s="30"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="38"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
       <c r="U4" s="9" t="s">
         <v>27</v>
       </c>
       <c r="V4" s="19"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="36"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
       <c r="D5" s="10"/>
@@ -833,50 +836,50 @@
       <c r="V5" s="19"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="34">
+      <c r="A6" s="29">
         <v>2</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="24"/>
+      <c r="D6" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28" t="s">
+      <c r="E6" s="24"/>
+      <c r="F6" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28" t="s">
+      <c r="G6" s="24"/>
+      <c r="H6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28" t="s">
+      <c r="I6" s="24"/>
+      <c r="J6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="28"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="37" t="s">
+      <c r="K6" s="24"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="37"/>
-      <c r="P6" s="28" t="s">
+      <c r="O6" s="32"/>
+      <c r="P6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28" t="s">
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="28"/>
+      <c r="S6" s="24"/>
       <c r="U6" s="8" t="s">
         <v>29</v>
       </c>
       <c r="V6" s="19"/>
     </row>
     <row r="7" spans="1:22" ht="15" thickBot="1">
-      <c r="A7" s="36"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="12" t="s">
         <v>19</v>
       </c>
@@ -886,13 +889,13 @@
       <c r="D7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="15" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="15" t="s">
         <v>19</v>
       </c>
       <c r="H7" s="12" t="s">
@@ -925,46 +928,50 @@
       <c r="V7" s="19"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28" t="s">
+      <c r="E8" s="24"/>
+      <c r="F8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28" t="s">
+      <c r="G8" s="24"/>
+      <c r="H8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="28"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="33" t="s">
+      <c r="I8" s="24"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33" t="s">
+      <c r="M8" s="38"/>
+      <c r="N8" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="33"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
       <c r="U8" s="20"/>
       <c r="V8" s="19"/>
     </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="30"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+    <row r="9" spans="1:22" ht="15" thickBot="1">
+      <c r="A9" s="36"/>
+      <c r="B9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>31</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -972,7 +979,7 @@
       <c r="H9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="2"/>
@@ -989,34 +996,34 @@
       <c r="V9" s="19"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="30"/>
-      <c r="B10" s="25" t="s">
+      <c r="A10" s="36"/>
+      <c r="B10" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="27" t="s">
+      <c r="C10" s="39"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="27"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
       <c r="U10" s="20"/>
       <c r="V10" s="19"/>
     </row>
     <row r="11" spans="1:22" ht="15" thickBot="1">
-      <c r="A11" s="31"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
       <c r="D11" s="10"/>
@@ -1038,26 +1045,27 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -1074,27 +1082,26 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="32">
   <si>
     <t>Неделя</t>
   </si>
@@ -242,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -250,9 +250,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -271,9 +268,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -334,7 +328,7 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -641,125 +635,125 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="3" width="8.88671875" style="6"/>
+    <col min="3" max="3" width="8.88671875" style="5"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
-    <col min="5" max="5" width="8.88671875" style="6"/>
+    <col min="5" max="5" width="8.88671875" style="5"/>
     <col min="6" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="8.88671875" style="6"/>
+    <col min="7" max="7" width="8.88671875" style="5"/>
     <col min="8" max="8" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.21875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" style="5" customWidth="1"/>
     <col min="10" max="10" width="7.21875" style="1" customWidth="1"/>
     <col min="11" max="11" width="7.88671875" style="1" customWidth="1"/>
     <col min="12" max="12" width="8.88671875" style="1"/>
-    <col min="13" max="13" width="8.88671875" style="6"/>
+    <col min="13" max="13" width="8.88671875" style="5"/>
     <col min="14" max="14" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.33203125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" style="5" customWidth="1"/>
     <col min="16" max="16" width="8.88671875" style="1"/>
-    <col min="17" max="17" width="8.88671875" style="6"/>
+    <col min="17" max="17" width="8.88671875" style="5"/>
     <col min="18" max="18" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" thickBot="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26" t="s">
+      <c r="G1" s="24"/>
+      <c r="H1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26" t="s">
+      <c r="I1" s="24"/>
+      <c r="J1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="23" t="s">
+      <c r="K1" s="24"/>
+      <c r="L1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23" t="s">
+      <c r="M1" s="21"/>
+      <c r="N1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23" t="s">
+      <c r="O1" s="21"/>
+      <c r="P1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23" t="s">
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="23"/>
-      <c r="U1" s="7" t="s">
+      <c r="S1" s="21"/>
+      <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="17"/>
+      <c r="V1" s="15"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="29">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24" t="s">
+      <c r="E2" s="22"/>
+      <c r="F2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="24" t="s">
+      <c r="G2" s="22"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24" t="s">
+      <c r="M2" s="22"/>
+      <c r="N2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="24"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="U2" s="18" t="s">
+      <c r="O2" s="22"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="U2" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="19"/>
+      <c r="V2" s="17"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="30"/>
+      <c r="A3" s="28"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="2"/>
@@ -773,213 +767,221 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="7"/>
-      <c r="U3" s="22" t="s">
+      <c r="S3" s="6"/>
+      <c r="U3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="V3" s="17"/>
+      <c r="V3" s="15"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="30"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="28" t="s">
+      <c r="A4" s="28"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="28"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="U4" s="9" t="s">
+      <c r="O4" s="26"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="U4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="V4" s="19"/>
+      <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="31"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="14"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="13"/>
       <c r="U5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="19"/>
+      <c r="V5" s="17"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="29">
+      <c r="A6" s="27">
         <v>2</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24" t="s">
+      <c r="C6" s="22"/>
+      <c r="D6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24" t="s">
+      <c r="E6" s="22"/>
+      <c r="F6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24" t="s">
+      <c r="I6" s="22"/>
+      <c r="J6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="32" t="s">
+      <c r="K6" s="22"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O6" s="32"/>
-      <c r="P6" s="24" t="s">
+      <c r="O6" s="30"/>
+      <c r="P6" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24" t="s">
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="U6" s="8" t="s">
+      <c r="S6" s="22"/>
+      <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="V6" s="19"/>
+      <c r="V6" s="17"/>
     </row>
     <row r="7" spans="1:22" ht="15" thickBot="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="29"/>
+      <c r="B7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="U7" s="21" t="s">
+      <c r="H7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="U7" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="V7" s="19"/>
+      <c r="V7" s="17"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24" t="s">
+      <c r="C8" s="22"/>
+      <c r="D8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24" t="s">
+      <c r="E8" s="22"/>
+      <c r="F8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24" t="s">
+      <c r="G8" s="22"/>
+      <c r="H8" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="38" t="s">
+      <c r="I8" s="22"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38" t="s">
+      <c r="M8" s="36"/>
+      <c r="N8" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="38"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="19"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="17"/>
     </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="13" t="s">
+    <row r="9" spans="1:22">
+      <c r="A9" s="34"/>
+      <c r="B9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="9" t="s">
+      <c r="D9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="2"/>
@@ -991,57 +993,61 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="2"/>
-      <c r="S9" s="7"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="19"/>
+      <c r="S9" s="6"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="17"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="36"/>
-      <c r="B10" s="39" t="s">
+      <c r="A10" s="34"/>
+      <c r="B10" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="41" t="s">
+      <c r="C10" s="37"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="41"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="19"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="17"/>
     </row>
     <row r="11" spans="1:22" ht="15" thickBot="1">
-      <c r="A11" s="37"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="14"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="57">

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="37">
   <si>
     <t>Неделя</t>
   </si>
@@ -112,6 +112,21 @@
   </si>
   <si>
     <t>ДЗ 3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>21.09</t>
+  </si>
+  <si>
+    <t>22.09</t>
+  </si>
+  <si>
+    <t>23.09</t>
+  </si>
+  <si>
+    <t>26.09</t>
   </si>
 </sst>
 </file>
@@ -172,7 +187,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -238,11 +253,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -280,7 +372,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -289,14 +384,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -307,35 +402,64 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -658,86 +782,86 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="33"/>
+      <c r="F1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="24"/>
-      <c r="L1" s="21" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21" t="s">
+      <c r="M1" s="32"/>
+      <c r="N1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21" t="s">
+      <c r="O1" s="32"/>
+      <c r="P1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21" t="s">
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="21"/>
+      <c r="S1" s="32"/>
       <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="V1" s="15"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="27">
+      <c r="A2" s="28">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="22" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22" t="s">
+      <c r="M2" s="23"/>
+      <c r="N2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="22"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
       <c r="U2" s="16" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="17"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="28"/>
+      <c r="A3" s="29"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -774,34 +898,34 @@
       <c r="V3" s="15"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="28"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="26" t="s">
+      <c r="A4" s="29"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
       <c r="U4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="29"/>
+      <c r="A5" s="30"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
@@ -830,270 +954,410 @@
       <c r="V5" s="17"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="27">
+      <c r="A6" s="37">
         <v>2</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22" t="s">
+      <c r="C6" s="46"/>
+      <c r="D6" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22" t="s">
+      <c r="E6" s="46"/>
+      <c r="F6" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22" t="s">
+      <c r="I6" s="46"/>
+      <c r="J6" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="22"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="O6" s="30"/>
-      <c r="P6" s="22" t="s">
+      <c r="K6" s="46"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22" t="s">
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="22"/>
+      <c r="S6" s="46"/>
       <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="V6" s="17"/>
     </row>
-    <row r="7" spans="1:22" ht="15" thickBot="1">
-      <c r="A7" s="29"/>
-      <c r="B7" s="11" t="s">
+    <row r="7" spans="1:22">
+      <c r="A7" s="38"/>
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="11" t="s">
+      <c r="L7" s="2"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
       <c r="U7" s="19" t="s">
         <v>30</v>
       </c>
       <c r="V7" s="17"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="38"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="31"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="V8" s="17"/>
+    </row>
+    <row r="9" spans="1:22" ht="15" thickBot="1">
+      <c r="A9" s="39"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="V9" s="17"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22" t="s">
+      <c r="C10" s="41"/>
+      <c r="D10" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22" t="s">
+      <c r="E10" s="41"/>
+      <c r="F10" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22" t="s">
+      <c r="G10" s="41"/>
+      <c r="H10" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="36" t="s">
+      <c r="I10" s="41"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36" t="s">
+      <c r="M10" s="23"/>
+      <c r="N10" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="36"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="17"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="34"/>
-      <c r="B9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="6"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="17"/>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="34"/>
-      <c r="B10" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="39"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="45"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="45"/>
       <c r="U10" s="18"/>
       <c r="V10" s="17"/>
     </row>
-    <row r="11" spans="1:22" ht="15" thickBot="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="12" t="s">
+    <row r="11" spans="1:22">
+      <c r="A11" s="36"/>
+      <c r="B11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="I11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="13"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="6"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="17"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="36"/>
+      <c r="B12" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="31"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="17"/>
+    </row>
+    <row r="13" spans="1:22" ht="15" thickBot="1">
+      <c r="A13" s="35"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="13"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="46"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" s="46"/>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" s="49"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" s="49"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="31"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+    </row>
+    <row r="17" spans="1:19" ht="15" thickBot="1">
+      <c r="A17" s="50"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
+  <mergeCells count="85">
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="N8:O8"/>
-    <mergeCell ref="R10:S10"/>
     <mergeCell ref="P8:Q8"/>
     <mergeCell ref="R8:S8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -1108,6 +1372,48 @@
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="38">
   <si>
     <t>Неделя</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>26.09</t>
+  </si>
+  <si>
+    <t>ДЗ 4</t>
   </si>
 </sst>
 </file>
@@ -372,10 +375,40 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -384,82 +417,52 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -782,26 +785,26 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33" t="s">
+      <c r="E1" s="35"/>
+      <c r="F1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="33"/>
+      <c r="K1" s="35"/>
       <c r="L1" s="32" t="s">
         <v>5</v>
       </c>
@@ -824,44 +827,44 @@
       <c r="V1" s="15"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="28">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="23" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23" t="s">
+      <c r="M2" s="33"/>
+      <c r="N2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
       <c r="U2" s="16" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="17"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="29"/>
+      <c r="A3" s="37"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -898,23 +901,23 @@
       <c r="V3" s="15"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="29"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
-      <c r="N4" s="31" t="s">
+      <c r="N4" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="31"/>
+      <c r="O4" s="26"/>
       <c r="P4" s="22"/>
       <c r="Q4" s="22"/>
       <c r="R4" s="22"/>
@@ -925,7 +928,7 @@
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="30"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
@@ -954,48 +957,48 @@
       <c r="V5" s="17"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="37">
+      <c r="A6" s="23">
         <v>2</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46" t="s">
+      <c r="C6" s="27"/>
+      <c r="D6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46" t="s">
+      <c r="G6" s="27"/>
+      <c r="H6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46" t="s">
+      <c r="I6" s="27"/>
+      <c r="J6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="46"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="46" t="s">
+      <c r="K6" s="27"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46" t="s">
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="46"/>
+      <c r="S6" s="27"/>
       <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="V6" s="17"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="38"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1008,7 +1011,7 @@
       <c r="E7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
@@ -1044,15 +1047,15 @@
       <c r="V7" s="17"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="38"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="31"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
@@ -1068,7 +1071,7 @@
       <c r="V8" s="17"/>
     </row>
     <row r="9" spans="1:22" ht="15" thickBot="1">
-      <c r="A9" s="39"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1090,44 +1093,44 @@
       <c r="V9" s="17"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="40" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="40" t="s">
+      <c r="E10" s="45"/>
+      <c r="F10" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="41"/>
-      <c r="H10" s="40" t="s">
+      <c r="G10" s="45"/>
+      <c r="H10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="41"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="23" t="s">
+      <c r="I10" s="45"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23" t="s">
+      <c r="M10" s="33"/>
+      <c r="N10" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="23"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="45"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="49"/>
       <c r="U10" s="18"/>
       <c r="V10" s="17"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="36"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="8" t="s">
         <v>31</v>
       </c>
@@ -1140,7 +1143,7 @@
       <c r="E11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -1166,25 +1169,25 @@
       <c r="V11" s="17"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="36"/>
-      <c r="B12" s="26" t="s">
+      <c r="A12" s="42"/>
+      <c r="B12" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
-      <c r="N12" s="31" t="s">
+      <c r="N12" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="O12" s="31"/>
+      <c r="O12" s="26"/>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="R12" s="22"/>
@@ -1193,7 +1196,7 @@
       <c r="V12" s="17"/>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1">
-      <c r="A13" s="35"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
@@ -1218,50 +1221,58 @@
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46" t="s">
+      <c r="C14" s="27"/>
+      <c r="D14" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46" t="s">
+      <c r="E14" s="27"/>
+      <c r="F14" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46" t="s">
+      <c r="G14" s="27"/>
+      <c r="H14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46" t="s">
+      <c r="I14" s="27"/>
+      <c r="J14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="46"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="46" t="s">
+      <c r="K14" s="27"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46" t="s">
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="S14" s="46"/>
+      <c r="S14" s="27"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="49"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="H15" s="8" t="s">
         <v>31</v>
       </c>
@@ -1278,21 +1289,21 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="49"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="31"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -1307,7 +1318,7 @@
       <c r="S16" s="22"/>
     </row>
     <row r="17" spans="1:19" ht="15" thickBot="1">
-      <c r="A17" s="50"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1329,55 +1340,26 @@
     </row>
   </sheetData>
   <mergeCells count="85">
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B6:C6"/>
@@ -1394,26 +1376,55 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -381,59 +381,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -452,6 +404,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -461,8 +416,53 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -785,86 +785,86 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="45"/>
+      <c r="D1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="45"/>
+      <c r="H1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35" t="s">
+      <c r="I1" s="45"/>
+      <c r="J1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="32" t="s">
+      <c r="K1" s="45"/>
+      <c r="L1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32" t="s">
+      <c r="M1" s="43"/>
+      <c r="N1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32" t="s">
+      <c r="O1" s="43"/>
+      <c r="P1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32" t="s">
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="32"/>
+      <c r="S1" s="43"/>
       <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="V1" s="15"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="36">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33" t="s">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33" t="s">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="33" t="s">
+      <c r="G2" s="32"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33" t="s">
+      <c r="M2" s="32"/>
+      <c r="N2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
       <c r="U2" s="16" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="17"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="37"/>
+      <c r="A3" s="39"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -901,23 +901,23 @@
       <c r="V3" s="15"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="37"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
-      <c r="N4" s="26" t="s">
+      <c r="N4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="26"/>
+      <c r="O4" s="23"/>
       <c r="P4" s="22"/>
       <c r="Q4" s="22"/>
       <c r="R4" s="22"/>
@@ -928,7 +928,7 @@
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="38"/>
+      <c r="A5" s="40"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
@@ -957,55 +957,55 @@
       <c r="V5" s="17"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="23">
+      <c r="A6" s="49">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27" t="s">
+      <c r="C6" s="24"/>
+      <c r="D6" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27" t="s">
+      <c r="E6" s="24"/>
+      <c r="F6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27" t="s">
+      <c r="G6" s="24"/>
+      <c r="H6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27" t="s">
+      <c r="I6" s="24"/>
+      <c r="J6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="27"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="27" t="s">
+      <c r="K6" s="24"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27" t="s">
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="27"/>
+      <c r="S6" s="24"/>
       <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="V6" s="17"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="24"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -1047,15 +1047,15 @@
       <c r="V7" s="17"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="24"/>
+      <c r="A8" s="50"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="23"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
@@ -1071,7 +1071,7 @@
       <c r="V8" s="17"/>
     </row>
     <row r="9" spans="1:22" ht="15" thickBot="1">
-      <c r="A9" s="25"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1093,45 +1093,45 @@
       <c r="V9" s="17"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="44" t="s">
+      <c r="C10" s="29"/>
+      <c r="D10" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="44" t="s">
+      <c r="E10" s="29"/>
+      <c r="F10" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="45"/>
-      <c r="H10" s="44" t="s">
+      <c r="G10" s="29"/>
+      <c r="H10" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="33" t="s">
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33" t="s">
+      <c r="M10" s="32"/>
+      <c r="N10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="33"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="49"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="34"/>
       <c r="U10" s="18"/>
       <c r="V10" s="17"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="42"/>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="26"/>
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -1149,7 +1149,7 @@
       <c r="G11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="I11" s="7" t="s">
@@ -1169,25 +1169,25 @@
       <c r="V11" s="17"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="42"/>
-      <c r="B12" s="50" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
-      <c r="N12" s="26" t="s">
+      <c r="N12" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="O12" s="26"/>
+      <c r="O12" s="23"/>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="R12" s="22"/>
@@ -1196,7 +1196,7 @@
       <c r="V12" s="17"/>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1">
-      <c r="A13" s="43"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
@@ -1221,44 +1221,44 @@
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27" t="s">
+      <c r="E14" s="24"/>
+      <c r="F14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27" t="s">
+      <c r="G14" s="24"/>
+      <c r="H14" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27" t="s">
+      <c r="I14" s="24"/>
+      <c r="J14" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="27"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="27" t="s">
+      <c r="K14" s="24"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27" t="s">
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="S14" s="27"/>
+      <c r="S14" s="24"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="30"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
@@ -1273,7 +1273,7 @@
       <c r="G15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="8" t="s">
@@ -1295,15 +1295,15 @@
       <c r="S15" s="2"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="30"/>
+      <c r="A16" s="47"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="26"/>
+      <c r="G16" s="23"/>
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -1318,7 +1318,7 @@
       <c r="S16" s="22"/>
     </row>
     <row r="17" spans="1:19" ht="15" thickBot="1">
-      <c r="A17" s="31"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1340,26 +1340,50 @@
     </row>
   </sheetData>
   <mergeCells count="85">
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B6:C6"/>
@@ -1376,55 +1400,31 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="P8:Q8"/>
     <mergeCell ref="R8:S8"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
   <si>
     <t>Неделя</t>
   </si>
@@ -130,6 +130,21 @@
   </si>
   <si>
     <t>ДЗ 4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>28.09</t>
+  </si>
+  <si>
+    <t>29.09</t>
+  </si>
+  <si>
+    <t>30.09</t>
+  </si>
+  <si>
+    <t>3.10</t>
   </si>
 </sst>
 </file>
@@ -337,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -381,11 +396,59 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -398,71 +461,35 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -785,86 +812,86 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45" t="s">
+      <c r="E1" s="35"/>
+      <c r="F1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="45"/>
-      <c r="L1" s="43" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43" t="s">
+      <c r="M1" s="32"/>
+      <c r="N1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43" t="s">
+      <c r="O1" s="32"/>
+      <c r="P1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43" t="s">
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="43"/>
+      <c r="S1" s="32"/>
       <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="V1" s="15"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="38">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="32" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32" t="s">
+      <c r="M2" s="33"/>
+      <c r="N2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="32"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
       <c r="U2" s="16" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="17"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="39"/>
+      <c r="A3" s="37"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -901,23 +928,23 @@
       <c r="V3" s="15"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="39"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
-      <c r="N4" s="23" t="s">
+      <c r="N4" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="23"/>
+      <c r="O4" s="26"/>
       <c r="P4" s="22"/>
       <c r="Q4" s="22"/>
       <c r="R4" s="22"/>
@@ -928,7 +955,7 @@
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="40"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
@@ -957,48 +984,48 @@
       <c r="V5" s="17"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="49">
+      <c r="A6" s="23">
         <v>2</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24" t="s">
+      <c r="C6" s="27"/>
+      <c r="D6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24" t="s">
+      <c r="G6" s="27"/>
+      <c r="H6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24" t="s">
+      <c r="I6" s="27"/>
+      <c r="J6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="24" t="s">
+      <c r="K6" s="27"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24" t="s">
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="24"/>
+      <c r="S6" s="27"/>
       <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="V6" s="17"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="50"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1023,7 +1050,7 @@
       <c r="I7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="7" t="s">
@@ -1047,15 +1074,15 @@
       <c r="V7" s="17"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="50"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="23"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
@@ -1071,7 +1098,7 @@
       <c r="V8" s="17"/>
     </row>
     <row r="9" spans="1:22" ht="15" thickBot="1">
-      <c r="A9" s="51"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1093,44 +1120,44 @@
       <c r="V9" s="17"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="28" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="28" t="s">
+      <c r="E10" s="45"/>
+      <c r="F10" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="28" t="s">
+      <c r="G10" s="45"/>
+      <c r="H10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="29"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="32" t="s">
+      <c r="I10" s="45"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32" t="s">
+      <c r="M10" s="33"/>
+      <c r="N10" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="32"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="34"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="51"/>
       <c r="U10" s="18"/>
       <c r="V10" s="17"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="26"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
@@ -1169,25 +1196,25 @@
       <c r="V11" s="17"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="26"/>
-      <c r="B12" s="35" t="s">
+      <c r="A12" s="42"/>
+      <c r="B12" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
-      <c r="N12" s="23" t="s">
+      <c r="N12" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="O12" s="23"/>
+      <c r="O12" s="26"/>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="R12" s="22"/>
@@ -1196,7 +1223,7 @@
       <c r="V12" s="17"/>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1">
-      <c r="A13" s="27"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
@@ -1221,44 +1248,44 @@
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24" t="s">
+      <c r="C14" s="27"/>
+      <c r="D14" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="27"/>
+      <c r="F14" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24" t="s">
+      <c r="G14" s="27"/>
+      <c r="H14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24" t="s">
+      <c r="I14" s="27"/>
+      <c r="J14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="24"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="24" t="s">
+      <c r="K14" s="27"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24" t="s">
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="S14" s="24"/>
+      <c r="S14" s="27"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="47"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
@@ -1289,21 +1316,29 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+      <c r="P15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="47"/>
+      <c r="A16" s="53"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="23"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -1318,7 +1353,7 @@
       <c r="S16" s="22"/>
     </row>
     <row r="17" spans="1:19" ht="15" thickBot="1">
-      <c r="A17" s="48"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1338,52 +1373,154 @@
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
     </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="45"/>
+      <c r="D18" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="45"/>
+      <c r="F18" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="45"/>
+      <c r="H18" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="O18" s="33"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="50"/>
+      <c r="S18" s="51"/>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" s="30"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="6"/>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="30"/>
+      <c r="B20" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="O20" s="26"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+    </row>
+    <row r="21" spans="1:19" ht="15" thickBot="1">
+      <c r="A21" s="31"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="55"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="13"/>
+    </row>
   </sheetData>
-  <mergeCells count="85">
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
+  <mergeCells count="104">
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B6:C6"/>
@@ -1400,31 +1537,50 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="44">
   <si>
     <t>Неделя</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>3.10</t>
+  </si>
+  <si>
+    <t>ДЗ 5</t>
   </si>
 </sst>
 </file>
@@ -393,9 +396,95 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -404,92 +493,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,86 +815,86 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="49"/>
+      <c r="D1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="49"/>
+      <c r="H1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35" t="s">
+      <c r="I1" s="49"/>
+      <c r="J1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="32" t="s">
+      <c r="K1" s="49"/>
+      <c r="L1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32" t="s">
+      <c r="M1" s="47"/>
+      <c r="N1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32" t="s">
+      <c r="O1" s="47"/>
+      <c r="P1" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32" t="s">
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="32"/>
+      <c r="S1" s="47"/>
       <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="V1" s="15"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="36">
+      <c r="A2" s="42">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33" t="s">
+      <c r="C2" s="27"/>
+      <c r="D2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33" t="s">
+      <c r="E2" s="27"/>
+      <c r="F2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="33" t="s">
+      <c r="G2" s="27"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33" t="s">
+      <c r="M2" s="27"/>
+      <c r="N2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
       <c r="U2" s="16" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="17"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="37"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -928,34 +931,34 @@
       <c r="V3" s="15"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="37"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="26" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
       <c r="U4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="38"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
@@ -984,48 +987,48 @@
       <c r="V5" s="17"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="23">
+      <c r="A6" s="53">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27" t="s">
+      <c r="E6" s="38"/>
+      <c r="F6" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27" t="s">
+      <c r="G6" s="38"/>
+      <c r="H6" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27" t="s">
+      <c r="I6" s="38"/>
+      <c r="J6" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="27"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="27" t="s">
+      <c r="K6" s="38"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27" t="s">
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="27"/>
+      <c r="S6" s="38"/>
       <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="V6" s="17"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="24"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1074,31 +1077,31 @@
       <c r="V7" s="17"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="24"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="26" t="s">
+      <c r="A8" s="54"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
       <c r="V8" s="17"/>
     </row>
     <row r="9" spans="1:22" ht="15" thickBot="1">
-      <c r="A9" s="25"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1120,54 +1123,54 @@
       <c r="V9" s="17"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="44" t="s">
+      <c r="C10" s="34"/>
+      <c r="D10" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="44" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="45"/>
-      <c r="H10" s="44" t="s">
+      <c r="G10" s="34"/>
+      <c r="H10" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="33" t="s">
+      <c r="I10" s="34"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33" t="s">
+      <c r="M10" s="27"/>
+      <c r="N10" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="33"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="51"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="29"/>
       <c r="U10" s="18"/>
       <c r="V10" s="17"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="42"/>
+      <c r="A11" s="40"/>
       <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -1196,34 +1199,34 @@
       <c r="V11" s="17"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="42"/>
-      <c r="B12" s="46" t="s">
+      <c r="A12" s="40"/>
+      <c r="B12" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="26" t="s">
+      <c r="C12" s="35"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="O12" s="26"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
       <c r="U12" s="18"/>
       <c r="V12" s="17"/>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1">
-      <c r="A13" s="43"/>
+      <c r="A13" s="41"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
@@ -1248,48 +1251,48 @@
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27" t="s">
+      <c r="C14" s="38"/>
+      <c r="D14" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27" t="s">
+      <c r="E14" s="38"/>
+      <c r="F14" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27" t="s">
+      <c r="G14" s="38"/>
+      <c r="H14" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27" t="s">
+      <c r="I14" s="38"/>
+      <c r="J14" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="27"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="27" t="s">
+      <c r="K14" s="38"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27" t="s">
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="S14" s="27"/>
+      <c r="S14" s="38"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="53"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="21"/>
@@ -1303,10 +1306,10 @@
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="8" t="s">
@@ -1330,30 +1333,30 @@
       </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="53"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="26" t="s">
+      <c r="A16" s="51"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="26"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
     </row>
     <row r="17" spans="1:19" ht="15" thickBot="1">
-      <c r="A17" s="54"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1374,42 +1377,42 @@
       <c r="S17" s="9"/>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="44" t="s">
+      <c r="C18" s="34"/>
+      <c r="D18" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="44" t="s">
+      <c r="E18" s="34"/>
+      <c r="F18" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="45"/>
-      <c r="H18" s="44" t="s">
+      <c r="G18" s="34"/>
+      <c r="H18" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="45"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="33" t="s">
+      <c r="I18" s="34"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33" t="s">
+      <c r="M18" s="27"/>
+      <c r="N18" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="33"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="51"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="29"/>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
@@ -1430,34 +1433,38 @@
       <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="30"/>
-      <c r="B20" s="46" t="s">
+      <c r="A20" s="31"/>
+      <c r="B20" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="26" t="s">
+      <c r="C20" s="35"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="O20" s="26"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="23"/>
     </row>
     <row r="21" spans="1:19" ht="15" thickBot="1">
-      <c r="A21" s="31"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="D21" s="9"/>
       <c r="E21" s="10"/>
       <c r="F21" s="9"/>
@@ -1468,8 +1475,8 @@
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="10"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="55"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="9"/>
@@ -1477,50 +1484,46 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B6:C6"/>
@@ -1541,46 +1544,50 @@
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="R18:S18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -355,7 +355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -376,9 +376,6 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -402,18 +399,83 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -427,71 +489,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -815,86 +812,86 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="35"/>
+      <c r="F1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="47" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47" t="s">
+      <c r="M1" s="32"/>
+      <c r="N1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47" t="s">
+      <c r="O1" s="32"/>
+      <c r="P1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47" t="s">
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="47"/>
+      <c r="S1" s="32"/>
       <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="15"/>
+      <c r="V1" s="14"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="42">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="27" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27" t="s">
+      <c r="M2" s="33"/>
+      <c r="N2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="27"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="U2" s="16" t="s">
+      <c r="O2" s="33"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="U2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="17"/>
+      <c r="V2" s="16"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="43"/>
+      <c r="A3" s="37"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -925,40 +922,40 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="2"/>
       <c r="S3" s="6"/>
-      <c r="U3" s="20" t="s">
+      <c r="U3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="V3" s="15"/>
+      <c r="V3" s="14"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="43"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="24" t="s">
+      <c r="A4" s="37"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="24"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
       <c r="U4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="V4" s="17"/>
+      <c r="V4" s="16"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="44"/>
+      <c r="A5" s="38"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
@@ -974,61 +971,61 @@
       <c r="N5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="14" t="s">
+      <c r="O5" s="13" t="s">
         <v>16</v>
       </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="9"/>
-      <c r="S5" s="13"/>
+      <c r="S5" s="12"/>
       <c r="U5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="17"/>
+      <c r="V5" s="16"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="53">
+      <c r="A6" s="25">
         <v>2</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38" t="s">
+      <c r="I6" s="23"/>
+      <c r="J6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="38"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="38" t="s">
+      <c r="K6" s="23"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38" t="s">
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="38"/>
+      <c r="S6" s="23"/>
       <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="V6" s="17"/>
+      <c r="V6" s="16"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="54"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1066,42 +1063,42 @@
       <c r="P7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="U7" s="19" t="s">
+      <c r="U7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="V7" s="17"/>
+      <c r="V7" s="16"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="54"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="24" t="s">
+      <c r="A8" s="26"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="V8" s="17"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="V8" s="16"/>
     </row>
     <row r="9" spans="1:22" ht="15" thickBot="1">
-      <c r="A9" s="55"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1120,47 +1117,47 @@
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
-      <c r="V9" s="17"/>
+      <c r="V9" s="16"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="33" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="33" t="s">
+      <c r="E10" s="45"/>
+      <c r="F10" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="33" t="s">
+      <c r="G10" s="45"/>
+      <c r="H10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="34"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="27" t="s">
+      <c r="I10" s="45"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27" t="s">
+      <c r="M10" s="33"/>
+      <c r="N10" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="27"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="29"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="17"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="51"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="16"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="40"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
@@ -1195,38 +1192,38 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="2"/>
       <c r="S11" s="6"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="16"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="40"/>
-      <c r="B12" s="35" t="s">
+      <c r="A12" s="42"/>
+      <c r="B12" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="24" t="s">
+      <c r="C12" s="46"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="O12" s="24"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="17"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="16"/>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1">
-      <c r="A13" s="41"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
@@ -1242,61 +1239,61 @@
       <c r="N13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="13" t="s">
         <v>19</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="9"/>
-      <c r="S13" s="13"/>
+      <c r="S13" s="12"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38" t="s">
+      <c r="I14" s="23"/>
+      <c r="J14" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="38"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="38" t="s">
+      <c r="K14" s="23"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="38" t="s">
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="S14" s="38"/>
+      <c r="S14" s="23"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="51"/>
+      <c r="A15" s="30"/>
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="3" t="s">
         <v>37</v>
       </c>
@@ -1333,30 +1330,30 @@
       </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="51"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24" t="s">
+      <c r="A16" s="30"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="24"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
     </row>
     <row r="17" spans="1:19" ht="15" thickBot="1">
-      <c r="A17" s="52"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1377,50 +1374,50 @@
       <c r="S17" s="9"/>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="33" t="s">
+      <c r="C18" s="45"/>
+      <c r="D18" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="33" t="s">
+      <c r="E18" s="45"/>
+      <c r="F18" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="33" t="s">
+      <c r="G18" s="45"/>
+      <c r="H18" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="34"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="27" t="s">
+      <c r="I18" s="45"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27" t="s">
+      <c r="M18" s="33"/>
+      <c r="N18" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="27"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="29"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="50"/>
+      <c r="S18" s="51"/>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="31"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -1433,33 +1430,33 @@
       <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="31"/>
-      <c r="B20" s="35" t="s">
+      <c r="A20" s="53"/>
+      <c r="B20" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="24" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="O20" s="24"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
     </row>
     <row r="21" spans="1:19" ht="15" thickBot="1">
-      <c r="A21" s="32"/>
-      <c r="B21" s="8" t="s">
+      <c r="A21" s="54"/>
+      <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -1475,55 +1472,50 @@
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="10"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="9"/>
-      <c r="S21" s="13"/>
+      <c r="S21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B6:C6"/>
@@ -1544,6 +1536,36 @@
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
@@ -1553,41 +1575,16 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="57">
   <si>
     <t>Неделя</t>
   </si>
@@ -148,6 +148,45 @@
   </si>
   <si>
     <t>ДЗ 5</t>
+  </si>
+  <si>
+    <t>ПР</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5.10</t>
+  </si>
+  <si>
+    <t>6.10</t>
+  </si>
+  <si>
+    <t>7.10</t>
+  </si>
+  <si>
+    <t>10.10</t>
+  </si>
+  <si>
+    <t>ДЗ 6</t>
+  </si>
+  <si>
+    <t>ДЗ 7</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>12.10</t>
+  </si>
+  <si>
+    <t>13.10</t>
+  </si>
+  <si>
+    <t>14.10</t>
+  </si>
+  <si>
+    <t>17.10</t>
   </si>
 </sst>
 </file>
@@ -396,15 +435,78 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -414,83 +516,20 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -785,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -812,86 +851,86 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35" t="s">
+      <c r="E1" s="51"/>
+      <c r="F1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="51"/>
+      <c r="H1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35" t="s">
+      <c r="I1" s="51"/>
+      <c r="J1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="32" t="s">
+      <c r="K1" s="51"/>
+      <c r="L1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32" t="s">
+      <c r="M1" s="49"/>
+      <c r="N1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32" t="s">
+      <c r="O1" s="49"/>
+      <c r="P1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32" t="s">
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="32"/>
+      <c r="S1" s="49"/>
       <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="V1" s="14"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="36">
+      <c r="A2" s="42">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33" t="s">
+      <c r="E2" s="36"/>
+      <c r="F2" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="33" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33" t="s">
+      <c r="M2" s="36"/>
+      <c r="N2" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
       <c r="U2" s="15" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="16"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="37"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -928,34 +967,34 @@
       <c r="V3" s="14"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="37"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
       <c r="N4" s="28" t="s">
         <v>11</v>
       </c>
       <c r="O4" s="28"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
       <c r="U4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="V4" s="16"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="38"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
@@ -984,48 +1023,48 @@
       <c r="V5" s="16"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="25">
+      <c r="A6" s="46">
         <v>2</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23" t="s">
+      <c r="C6" s="37"/>
+      <c r="D6" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23" t="s">
+      <c r="E6" s="37"/>
+      <c r="F6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23" t="s">
+      <c r="G6" s="37"/>
+      <c r="H6" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23" t="s">
+      <c r="I6" s="37"/>
+      <c r="J6" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="23" t="s">
+      <c r="K6" s="37"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23" t="s">
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="23"/>
+      <c r="S6" s="37"/>
       <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="V6" s="16"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="26"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1074,31 +1113,31 @@
       <c r="V7" s="16"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="26"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
+      <c r="A8" s="47"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
       <c r="F8" s="28" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="28"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
       <c r="V8" s="16"/>
     </row>
     <row r="9" spans="1:22" ht="15" thickBot="1">
-      <c r="A9" s="27"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1120,44 +1159,44 @@
       <c r="V9" s="16"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="44" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="44" t="s">
+      <c r="E10" s="33"/>
+      <c r="F10" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="45"/>
-      <c r="H10" s="44" t="s">
+      <c r="G10" s="33"/>
+      <c r="H10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="33" t="s">
+      <c r="I10" s="33"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33" t="s">
+      <c r="M10" s="36"/>
+      <c r="N10" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="33"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="51"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="23"/>
       <c r="U10" s="17"/>
       <c r="V10" s="16"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="42"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
@@ -1196,34 +1235,34 @@
       <c r="V11" s="16"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="42"/>
-      <c r="B12" s="46" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
       <c r="N12" s="28" t="s">
         <v>23</v>
       </c>
       <c r="O12" s="28"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
       <c r="U12" s="17"/>
       <c r="V12" s="16"/>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1">
-      <c r="A13" s="43"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
@@ -1248,44 +1287,44 @@
       <c r="S13" s="12"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23" t="s">
+      <c r="C14" s="37"/>
+      <c r="D14" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23" t="s">
+      <c r="E14" s="37"/>
+      <c r="F14" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23" t="s">
+      <c r="G14" s="37"/>
+      <c r="H14" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23" t="s">
+      <c r="I14" s="37"/>
+      <c r="J14" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="23"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="23" t="s">
+      <c r="K14" s="37"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23" t="s">
+      <c r="Q14" s="37"/>
+      <c r="R14" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="S14" s="23"/>
+      <c r="S14" s="37"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="30"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
@@ -1330,30 +1369,30 @@
       </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="30"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
       <c r="F16" s="28" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
     </row>
     <row r="17" spans="1:19" ht="15" thickBot="1">
-      <c r="A17" s="31"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1374,48 +1413,56 @@
       <c r="S17" s="9"/>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="44" t="s">
+      <c r="C18" s="33"/>
+      <c r="D18" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="44" t="s">
+      <c r="E18" s="33"/>
+      <c r="F18" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="45"/>
-      <c r="H18" s="44" t="s">
+      <c r="G18" s="33"/>
+      <c r="H18" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="45"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="33" t="s">
+      <c r="I18" s="33"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33" t="s">
+      <c r="M18" s="36"/>
+      <c r="N18" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="33"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="51"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="23"/>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="53"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
       <c r="J19" s="2"/>
@@ -1430,32 +1477,32 @@
       <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="53"/>
-      <c r="B20" s="46" t="s">
+      <c r="A20" s="39"/>
+      <c r="B20" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
       <c r="N20" s="28" t="s">
         <v>42</v>
       </c>
       <c r="O20" s="28"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
     </row>
     <row r="21" spans="1:19" ht="15" thickBot="1">
-      <c r="A21" s="54"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -1472,50 +1519,296 @@
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="10"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
+      <c r="N21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="P21" s="9"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="9"/>
       <c r="S21" s="12"/>
     </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" s="37"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="S22" s="37"/>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="39"/>
+      <c r="B23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="39"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="37"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+    </row>
+    <row r="25" spans="1:19" ht="15" thickBot="1">
+      <c r="A25" s="40"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="33"/>
+      <c r="D26" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="33"/>
+      <c r="F26" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="33"/>
+      <c r="H26" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="33"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="O26" s="36"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="23"/>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="30"/>
+      <c r="B27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="6"/>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" s="30"/>
+      <c r="B28" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" s="28"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+    </row>
+    <row r="29" spans="1:19" ht="15" thickBot="1">
+      <c r="A29" s="31"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="104">
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
+  <mergeCells count="142">
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B6:C6"/>
@@ -1536,55 +1829,83 @@
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R28:S28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="58">
   <si>
     <t>Неделя</t>
   </si>
@@ -187,6 +187,9 @@
   </si>
   <si>
     <t>17.10</t>
+  </si>
+  <si>
+    <t>ДЗ 8</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1215,7 @@
       <c r="F11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="H11" s="3" t="s">
@@ -1348,7 +1351,7 @@
       <c r="J15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="L15" s="4"/>
@@ -1457,7 +1460,7 @@
       <c r="E19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="3" t="s">
         <v>43</v>
       </c>
       <c r="G19" s="8" t="s">
@@ -1506,7 +1509,7 @@
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="9"/>
@@ -1569,24 +1572,24 @@
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="39"/>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20"/>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="3" t="s">
         <v>50</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J23" s="20"/>
@@ -1689,7 +1692,7 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="30"/>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -1697,9 +1700,13 @@
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="8" t="s">
+      <c r="F27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>43</v>
       </c>
       <c r="I27" s="8" t="s">

--- a/Задания.xlsx
+++ b/Задания.xlsx
@@ -438,27 +438,92 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -468,71 +533,6 @@
     <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -854,86 +854,86 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51" t="s">
+      <c r="C1" s="40"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51" t="s">
+      <c r="E1" s="40"/>
+      <c r="F1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51" t="s">
+      <c r="G1" s="40"/>
+      <c r="H1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51" t="s">
+      <c r="I1" s="40"/>
+      <c r="J1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="51"/>
-      <c r="L1" s="49" t="s">
+      <c r="K1" s="40"/>
+      <c r="L1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49" t="s">
+      <c r="M1" s="37"/>
+      <c r="N1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49" t="s">
+      <c r="O1" s="37"/>
+      <c r="P1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49" t="s">
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="49"/>
+      <c r="S1" s="37"/>
       <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="V1" s="14"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="42">
+      <c r="A2" s="41">
         <v>1</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36" t="s">
+      <c r="E2" s="38"/>
+      <c r="F2" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="36" t="s">
+      <c r="G2" s="38"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36" t="s">
+      <c r="M2" s="38"/>
+      <c r="N2" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="36"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
       <c r="U2" s="15" t="s">
         <v>24</v>
       </c>
       <c r="V2" s="16"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="43"/>
+      <c r="A3" s="42"/>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
@@ -970,34 +970,34 @@
       <c r="V3" s="14"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="43"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
       <c r="N4" s="28" t="s">
         <v>11</v>
       </c>
       <c r="O4" s="28"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
       <c r="U4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="V4" s="16"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
-      <c r="A5" s="44"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10"/>
       <c r="D5" s="9"/>
@@ -1026,48 +1026,48 @@
       <c r="V5" s="16"/>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="46">
+      <c r="A6" s="45">
         <v>2</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37" t="s">
+      <c r="G6" s="23"/>
+      <c r="H6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37" t="s">
+      <c r="I6" s="23"/>
+      <c r="J6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="37"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="37" t="s">
+      <c r="K6" s="23"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37" t="s">
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="S6" s="37"/>
+      <c r="S6" s="23"/>
       <c r="U6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="V6" s="16"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="47"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1116,31 +1116,31 @@
       <c r="V7" s="16"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="47"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="A8" s="46"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="28" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="28"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
       <c r="V8" s="16"/>
     </row>
     <row r="9" spans="1:22" ht="15" thickBot="1">
-      <c r="A9" s="48"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1162,7 +1162,7 @@
       <c r="V9" s="16"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="29" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="32" t="s">
@@ -1181,25 +1181,25 @@
         <v>20</v>
       </c>
       <c r="I10" s="33"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="36" t="s">
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36" t="s">
+      <c r="M10" s="38"/>
+      <c r="N10" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="36"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="23"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="51"/>
       <c r="U10" s="17"/>
       <c r="V10" s="16"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="53"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
@@ -1238,34 +1238,34 @@
       <c r="V11" s="16"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="53"/>
-      <c r="B12" s="24" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
       <c r="N12" s="28" t="s">
         <v>23</v>
       </c>
       <c r="O12" s="28"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
-      <c r="S12" s="27"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
       <c r="U12" s="17"/>
       <c r="V12" s="16"/>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1">
-      <c r="A13" s="54"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="9"/>
@@ -1290,44 +1290,44 @@
       <c r="S13" s="12"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37" t="s">
+      <c r="I14" s="23"/>
+      <c r="J14" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="37"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="37" t="s">
+      <c r="K14" s="23"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37" t="s">
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="S14" s="37"/>
+      <c r="S14" s="23"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="39"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
@@ -1364,7 +1364,7 @@
       <c r="Q15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="R15" s="8" t="s">
+      <c r="R15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="S15" s="8" t="s">
@@ -1372,30 +1372,30 @@
       </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="39"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="28" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
     </row>
     <row r="17" spans="1:19" ht="15" thickBot="1">
-      <c r="A17" s="40"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1416,7 +1416,7 @@
       <c r="S17" s="9"/>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="25" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="32" t="s">
@@ -1435,23 +1435,23 @@
         <v>39</v>
       </c>
       <c r="I18" s="33"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="36" t="s">
+      <c r="J18" s="48"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36" t="s">
+      <c r="M18" s="38"/>
+      <c r="N18" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="O18" s="36"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="23"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="50"/>
+      <c r="S18" s="51"/>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="39"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
       <c r="D19" s="8" t="s">
@@ -1480,32 +1480,32 @@
       <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="39"/>
-      <c r="B20" s="24" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
       <c r="N20" s="28" t="s">
         <v>42</v>
       </c>
       <c r="O20" s="28"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
     </row>
     <row r="21" spans="1:19" ht="15" thickBot="1">
-      <c r="A21" s="40"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
@@ -1534,44 +1534,44 @@
       <c r="S21" s="12"/>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37" t="s">
+      <c r="C22" s="23"/>
+      <c r="D22" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37" t="s">
+      <c r="E22" s="23"/>
+      <c r="F22" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37" t="s">
+      <c r="G22" s="23"/>
+      <c r="H22" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37" t="s">
+      <c r="I22" s="23"/>
+      <c r="J22" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="37"/>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="37" t="s">
+      <c r="K22" s="23"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37" t="s">
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="S22" s="37"/>
+      <c r="S22" s="23"/>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="39"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="3" t="s">
         <v>50</v>
       </c>
@@ -1608,30 +1608,30 @@
       <c r="S23" s="20"/>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="39"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="37" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="22"/>
     </row>
     <row r="25" spans="1:19" ht="15" thickBot="1">
-      <c r="A25" s="40"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -1656,7 +1656,7 @@
       <c r="S25" s="9"/>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="52" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="32" t="s">
@@ -1675,23 +1675,23 @@
         <v>53</v>
       </c>
       <c r="I26" s="33"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="36" t="s">
+      <c r="J26" s="48"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36" t="s">
+      <c r="M26" s="38"/>
+      <c r="N26" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="O26" s="36"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="23"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="51"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="51"/>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="30"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="3" t="s">
         <v>51</v>
       </c>
@@ -1724,32 +1724,32 @@
       <c r="S27" s="6"/>
     </row>
     <row r="28" spans="1:19">
-      <c r="A28" s="30"/>
-      <c r="B28" s="24" t="s">
+      <c r="A28" s="53"/>
+      <c r="B28" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
       <c r="N28" s="28" t="s">
         <v>56</v>
       </c>
       <c r="O28" s="28"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
     </row>
     <row r="29" spans="1:19" ht="15" thickBot="1">
-      <c r="A29" s="31"/>
+      <c r="A29" s="54"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
       <c r="D29" s="10"/>
@@ -1771,51 +1771,79 @@
     </row>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="R8:S8"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B6:C6"/>
@@ -1840,79 +1868,51 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
